--- a/data/信用债发行汇总_2026-07-27.xlsx
+++ b/data/信用债发行汇总_2026-07-27.xlsx
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>07-27 18:00</t>
+          <t>07-27 19:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>2.2952</t>
+          <t>2.2945</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07-27 18:00</t>
+          <t>07-27 19:00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2.2952</t>
+          <t>2.2945</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
